--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/cargas nuevas/3PC Contratos CM - Octubre 2026.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/cargas nuevas/3PC Contratos CM - Octubre 2026.xlsx
@@ -500,16 +500,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>159900004</v>
+        <v>153002676</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YV2RB40C8RE900069</t>
+          <t>YV2RB40C8RE214269</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>E900069</t>
+          <t>E214269</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -544,16 +544,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>159900010</v>
+        <v>153006213</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9BVXT4ZC3TA900051</t>
+          <t>9BVXT4ZC3TA475203</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A900051</t>
+          <t>A475203</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -588,16 +588,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>159900007</v>
+        <v>153005234</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9BVK20AB4TA900003</t>
+          <t>9BVK20AB4TA420236</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A900003</t>
+          <t>A420236</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -632,16 +632,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>159900005</v>
+        <v>153003255</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YV2RT4ZC4PE900088</t>
+          <t>YV2RT4ZC4PE665244</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E900088</t>
+          <t>E665244</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -676,16 +676,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>159900014</v>
+        <v>153009582</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9BVTE2AD2PE900044</t>
+          <t>9BVTE2AD2PE916072</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E900044</t>
+          <t>E916072</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -720,16 +720,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>159900002</v>
+        <v>153001647</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9BVRT4ZC3SE900028</t>
+          <t>9BVRT4ZC3SE936351</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E900028</t>
+          <t>E936351</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -764,16 +764,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>159900013</v>
+        <v>153009005</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9BVRT4ZA4TE900021</t>
+          <t>9BVRT4ZA4TE816190</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>E900021</t>
+          <t>E816190</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -808,16 +808,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>159900003</v>
+        <v>153002519</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9BVRT4ZB4PA900025</t>
+          <t>9BVRT4ZB4PA302713</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A900025</t>
+          <t>A302713</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -852,16 +852,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>159900011</v>
+        <v>153006836</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9BVRT4ZD6TE900039</t>
+          <t>9BVRT4ZD6TE808448</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>E900039</t>
+          <t>E808448</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -896,16 +896,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>159900009</v>
+        <v>153005736</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>YV2XT4ZB3PA900118</t>
+          <t>YV2XT4ZB3PA339996</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A900118</t>
+          <t>A339996</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -940,16 +940,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>159900001</v>
+        <v>153001492</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9BVRT4ZC4SA900029</t>
+          <t>9BVRT4ZC4SA836169</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A900029</t>
+          <t>A836169</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -984,16 +984,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>159900015</v>
+        <v>153010411</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YV2XT4ZD1SE900124</t>
+          <t>YV2XT4ZD1SE547662</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>E900124</t>
+          <t>E547662</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1028,16 +1028,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>159900016</v>
+        <v>153010587</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>YV2RB40B2PE900066</t>
+          <t>YV2RB40B2PE367359</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>E900066</t>
+          <t>E367359</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1072,16 +1072,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>159900017</v>
+        <v>153010592</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9BVK20AD9RA900008</t>
+          <t>9BVK20AD9RA673942</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A900008</t>
+          <t>A673942</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1116,16 +1116,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>159900018</v>
+        <v>153010604</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YV2RT4ZA6TE900083</t>
+          <t>YV2RT4ZA6TE904512</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>E900083</t>
+          <t>E904512</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1160,16 +1160,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>159900019</v>
+        <v>153010605</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YV2XT4ZC7TE900123</t>
+          <t>YV2XT4ZC7TE904873</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>E900123</t>
+          <t>E904873</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
